--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,36 +714,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>976000</v>
+        <v>1279500</v>
       </c>
       <c r="E8" s="3">
-        <v>912100</v>
+        <v>973400</v>
       </c>
       <c r="F8" s="3">
-        <v>424400</v>
+        <v>909600</v>
       </c>
       <c r="G8" s="3">
-        <v>136100</v>
+        <v>423300</v>
       </c>
       <c r="H8" s="3">
-        <v>104000</v>
+        <v>135700</v>
       </c>
       <c r="I8" s="3">
-        <v>40000</v>
+        <v>103700</v>
       </c>
       <c r="J8" s="3">
+        <v>39800</v>
+      </c>
+      <c r="K8" s="3">
         <v>11200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,36 +756,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>127700</v>
+        <v>196400</v>
       </c>
       <c r="E9" s="3">
-        <v>154600</v>
+        <v>127300</v>
       </c>
       <c r="F9" s="3">
-        <v>89200</v>
+        <v>154200</v>
       </c>
       <c r="G9" s="3">
-        <v>36100</v>
+        <v>89000</v>
       </c>
       <c r="H9" s="3">
-        <v>32000</v>
+        <v>36000</v>
       </c>
       <c r="I9" s="3">
-        <v>14000</v>
+        <v>31900</v>
       </c>
       <c r="J9" s="3">
+        <v>13900</v>
+      </c>
+      <c r="K9" s="3">
         <v>5800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,36 +798,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>848300</v>
+        <v>1083100</v>
       </c>
       <c r="E10" s="3">
-        <v>757500</v>
+        <v>846000</v>
       </c>
       <c r="F10" s="3">
-        <v>335200</v>
+        <v>755400</v>
       </c>
       <c r="G10" s="3">
-        <v>100000</v>
+        <v>334300</v>
       </c>
       <c r="H10" s="3">
-        <v>72000</v>
+        <v>99700</v>
       </c>
       <c r="I10" s="3">
-        <v>26000</v>
+        <v>71800</v>
       </c>
       <c r="J10" s="3">
+        <v>25900</v>
+      </c>
+      <c r="K10" s="3">
         <v>5400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,35 +861,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>156700</v>
+        <v>184200</v>
       </c>
       <c r="E12" s="3">
-        <v>103200</v>
+        <v>156200</v>
       </c>
       <c r="F12" s="3">
-        <v>65800</v>
+        <v>103000</v>
       </c>
       <c r="G12" s="3">
-        <v>33600</v>
+        <v>65600</v>
       </c>
       <c r="H12" s="3">
-        <v>19400</v>
+        <v>33500</v>
       </c>
       <c r="I12" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J12" s="3">
         <v>12200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7900</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,9 +942,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,9 +984,12 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,35 +1044,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>518500</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>504100</v>
+        <v>517100</v>
       </c>
       <c r="F17" s="3">
-        <v>236200</v>
+        <v>502700</v>
       </c>
       <c r="G17" s="3">
-        <v>112000</v>
+        <v>235600</v>
       </c>
       <c r="H17" s="3">
-        <v>77200</v>
+        <v>111700</v>
       </c>
       <c r="I17" s="3">
-        <v>38900</v>
+        <v>77000</v>
       </c>
       <c r="J17" s="3">
+        <v>38800</v>
+      </c>
+      <c r="K17" s="3">
         <v>25300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,36 +1083,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>457500</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>408000</v>
+        <v>456200</v>
       </c>
       <c r="F18" s="3">
-        <v>188200</v>
+        <v>406900</v>
       </c>
       <c r="G18" s="3">
-        <v>24100</v>
+        <v>187700</v>
       </c>
       <c r="H18" s="3">
-        <v>26800</v>
+        <v>24000</v>
       </c>
       <c r="I18" s="3">
+        <v>26700</v>
+      </c>
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,35 +1146,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-27000</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,36 +1185,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>437500</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>413000</v>
+        <v>434000</v>
       </c>
       <c r="F21" s="3">
-        <v>189400</v>
+        <v>410700</v>
       </c>
       <c r="G21" s="3">
-        <v>24900</v>
+        <v>187500</v>
       </c>
       <c r="H21" s="3">
-        <v>26800</v>
+        <v>23800</v>
       </c>
       <c r="I21" s="3">
-        <v>1000</v>
+        <v>26200</v>
       </c>
       <c r="J21" s="3">
+        <v>900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-13900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,9 +1227,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1230,36 +1269,39 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>430500</v>
+        <v>644400</v>
       </c>
       <c r="E23" s="3">
-        <v>408300</v>
+        <v>429400</v>
       </c>
       <c r="F23" s="3">
-        <v>185900</v>
+        <v>407200</v>
       </c>
       <c r="G23" s="3">
-        <v>22800</v>
+        <v>185400</v>
       </c>
       <c r="H23" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I23" s="3">
         <v>25700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1311,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>53100</v>
+        <v>95700</v>
       </c>
       <c r="E24" s="3">
-        <v>48100</v>
+        <v>52900</v>
       </c>
       <c r="F24" s="3">
+        <v>48000</v>
+      </c>
+      <c r="G24" s="3">
         <v>16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1700</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,36 +1395,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>377500</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>360200</v>
+        <v>376400</v>
       </c>
       <c r="F26" s="3">
-        <v>169900</v>
+        <v>359300</v>
       </c>
       <c r="G26" s="3">
+        <v>169500</v>
+      </c>
+      <c r="H26" s="3">
         <v>21200</v>
       </c>
-      <c r="H26" s="3">
-        <v>17800</v>
-      </c>
       <c r="I26" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,36 +1437,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>375200</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>360200</v>
+        <v>374200</v>
       </c>
       <c r="F27" s="3">
-        <v>169900</v>
+        <v>359300</v>
       </c>
       <c r="G27" s="3">
-        <v>18400</v>
+        <v>169500</v>
       </c>
       <c r="H27" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I27" s="3">
         <v>4700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-7200</v>
-      </c>
       <c r="J27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-14900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,36 +1647,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>27000</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,36 +1689,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>375200</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>360200</v>
+        <v>374200</v>
       </c>
       <c r="F33" s="3">
-        <v>169900</v>
+        <v>359300</v>
       </c>
       <c r="G33" s="3">
-        <v>18400</v>
+        <v>169500</v>
       </c>
       <c r="H33" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I33" s="3">
         <v>4700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-7200</v>
-      </c>
       <c r="J33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-14900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,36 +1773,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>375200</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>360200</v>
+        <v>374200</v>
       </c>
       <c r="F35" s="3">
-        <v>169900</v>
+        <v>359300</v>
       </c>
       <c r="G35" s="3">
-        <v>18400</v>
+        <v>169500</v>
       </c>
       <c r="H35" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I35" s="3">
         <v>4700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-7200</v>
-      </c>
       <c r="J35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-14900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,41 +1815,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,35 +1901,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7142000</v>
+        <v>6303400</v>
       </c>
       <c r="E41" s="3">
-        <v>7600300</v>
+        <v>7122500</v>
       </c>
       <c r="F41" s="3">
-        <v>5579100</v>
+        <v>7579600</v>
       </c>
       <c r="G41" s="3">
-        <v>1910500</v>
+        <v>5563800</v>
       </c>
       <c r="H41" s="3">
-        <v>1536600</v>
+        <v>1905300</v>
       </c>
       <c r="I41" s="3">
-        <v>968100</v>
+        <v>1532400</v>
       </c>
       <c r="J41" s="3">
+        <v>965400</v>
+      </c>
+      <c r="K41" s="3">
         <v>451800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,38 +1940,41 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>91400</v>
+        <v>415900</v>
       </c>
       <c r="E42" s="3">
-        <v>163600</v>
+        <v>91100</v>
       </c>
       <c r="F42" s="3">
-        <v>38500</v>
+        <v>163100</v>
       </c>
       <c r="G42" s="3">
+        <v>38400</v>
+      </c>
+      <c r="H42" s="3">
         <v>12000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1893,36 +1982,39 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4682000</v>
+        <v>5455700</v>
       </c>
       <c r="E43" s="3">
-        <v>5135500</v>
+        <v>4669200</v>
       </c>
       <c r="F43" s="3">
-        <v>1040100</v>
+        <v>5121500</v>
       </c>
       <c r="G43" s="3">
-        <v>237900</v>
+        <v>1037200</v>
       </c>
       <c r="H43" s="3">
-        <v>107300</v>
+        <v>237300</v>
       </c>
       <c r="I43" s="3">
-        <v>51300</v>
+        <v>107000</v>
       </c>
       <c r="J43" s="3">
+        <v>51100</v>
+      </c>
+      <c r="K43" s="3">
         <v>104400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,36 +2066,39 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E45" s="3">
         <v>14500</v>
       </c>
-      <c r="E45" s="3">
-        <v>9700</v>
-      </c>
       <c r="F45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2010,38 +2108,41 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11929900</v>
+        <v>12199500</v>
       </c>
       <c r="E46" s="3">
-        <v>12909000</v>
+        <v>11897300</v>
       </c>
       <c r="F46" s="3">
-        <v>6659000</v>
+        <v>12873800</v>
       </c>
       <c r="G46" s="3">
-        <v>2162000</v>
+        <v>6640900</v>
       </c>
       <c r="H46" s="3">
-        <v>1652600</v>
+        <v>2156100</v>
       </c>
       <c r="I46" s="3">
-        <v>1019800</v>
+        <v>1648100</v>
       </c>
       <c r="J46" s="3">
+        <v>1017000</v>
+      </c>
+      <c r="K46" s="3">
         <v>556800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
+      <c r="L46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -2049,36 +2150,39 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>35400</v>
+        <v>32900</v>
       </c>
       <c r="E47" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F47" s="3">
         <v>3000</v>
       </c>
-      <c r="F47" s="3">
-        <v>2413200</v>
-      </c>
       <c r="G47" s="3">
-        <v>537700</v>
+        <v>2406600</v>
       </c>
       <c r="H47" s="3">
-        <v>395700</v>
+        <v>536300</v>
       </c>
       <c r="I47" s="3">
-        <v>372800</v>
+        <v>394600</v>
       </c>
       <c r="J47" s="3">
+        <v>371800</v>
+      </c>
+      <c r="K47" s="3">
         <v>16900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2088,36 +2192,39 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>43900</v>
+        <v>28600</v>
       </c>
       <c r="E48" s="3">
-        <v>53800</v>
+        <v>43800</v>
       </c>
       <c r="F48" s="3">
-        <v>40700</v>
+        <v>53600</v>
       </c>
       <c r="G48" s="3">
-        <v>35800</v>
+        <v>40500</v>
       </c>
       <c r="H48" s="3">
+        <v>35700</v>
+      </c>
+      <c r="I48" s="3">
         <v>2900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,26 +2234,29 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3">
         <v>7000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>200</v>
       </c>
       <c r="I49" s="3">
         <v>200</v>
@@ -2154,8 +2264,8 @@
       <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>200</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,36 +2360,39 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>98100</v>
+        <v>156800</v>
       </c>
       <c r="E52" s="3">
-        <v>48200</v>
+        <v>97800</v>
       </c>
       <c r="F52" s="3">
-        <v>30600</v>
+        <v>48000</v>
       </c>
       <c r="G52" s="3">
+        <v>30500</v>
+      </c>
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="H52" s="3">
-        <v>7700</v>
-      </c>
       <c r="I52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J52" s="3">
         <v>5900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,36 +2444,39 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12114300</v>
+        <v>12417800</v>
       </c>
       <c r="E54" s="3">
-        <v>13016200</v>
+        <v>12081200</v>
       </c>
       <c r="F54" s="3">
-        <v>9144800</v>
+        <v>12980700</v>
       </c>
       <c r="G54" s="3">
-        <v>2743300</v>
+        <v>9119800</v>
       </c>
       <c r="H54" s="3">
-        <v>2059100</v>
+        <v>2735800</v>
       </c>
       <c r="I54" s="3">
-        <v>1400300</v>
+        <v>2053500</v>
       </c>
       <c r="J54" s="3">
+        <v>1396500</v>
+      </c>
+      <c r="K54" s="3">
         <v>579100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,35 +2525,36 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>8854900</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3">
-        <v>8604200</v>
+        <v>8830700</v>
       </c>
       <c r="F57" s="3">
-        <v>6527500</v>
+        <v>8580700</v>
       </c>
       <c r="G57" s="3">
-        <v>2169400</v>
+        <v>6509700</v>
       </c>
       <c r="H57" s="3">
-        <v>1695400</v>
+        <v>2163500</v>
       </c>
       <c r="I57" s="3">
-        <v>1070800</v>
+        <v>1690800</v>
       </c>
       <c r="J57" s="3">
+        <v>1067900</v>
+      </c>
+      <c r="K57" s="3">
         <v>531900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,36 +2564,39 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>318000</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
-        <v>1387700</v>
+        <v>317100</v>
       </c>
       <c r="F58" s="3">
-        <v>1401900</v>
+        <v>1383900</v>
       </c>
       <c r="G58" s="3">
-        <v>188300</v>
+        <v>1398000</v>
       </c>
       <c r="H58" s="3">
-        <v>202100</v>
+        <v>187800</v>
       </c>
       <c r="I58" s="3">
-        <v>197700</v>
+        <v>201500</v>
       </c>
       <c r="J58" s="3">
+        <v>197200</v>
+      </c>
+      <c r="K58" s="3">
         <v>20700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,36 +2606,39 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>252400</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>311800</v>
+        <v>251700</v>
       </c>
       <c r="F59" s="3">
-        <v>121900</v>
+        <v>311000</v>
       </c>
       <c r="G59" s="3">
-        <v>36700</v>
+        <v>121600</v>
       </c>
       <c r="H59" s="3">
+        <v>36600</v>
+      </c>
+      <c r="I59" s="3">
         <v>20600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,38 +2648,41 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>9425300</v>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E60" s="3">
-        <v>10303700</v>
+        <v>9399500</v>
       </c>
       <c r="F60" s="3">
-        <v>8051300</v>
+        <v>10275600</v>
       </c>
       <c r="G60" s="3">
-        <v>2394400</v>
+        <v>8029400</v>
       </c>
       <c r="H60" s="3">
-        <v>1918100</v>
+        <v>2387900</v>
       </c>
       <c r="I60" s="3">
-        <v>1278500</v>
+        <v>1912800</v>
       </c>
       <c r="J60" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="K60" s="3">
         <v>557200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -2551,9 +2690,12 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2576,11 +2718,11 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>4100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2590,26 +2732,29 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>14800</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
-        <v>22400</v>
+        <v>14700</v>
       </c>
       <c r="F62" s="3">
-        <v>28500</v>
+        <v>22300</v>
       </c>
       <c r="G62" s="3">
-        <v>22100</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>28400</v>
+      </c>
+      <c r="H62" s="3">
+        <v>22000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2620,8 +2765,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,36 +2900,39 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>9440100</v>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E66" s="3">
-        <v>10326100</v>
+        <v>9414300</v>
       </c>
       <c r="F66" s="3">
-        <v>8079800</v>
+        <v>10297900</v>
       </c>
       <c r="G66" s="3">
-        <v>2416600</v>
+        <v>8057800</v>
       </c>
       <c r="H66" s="3">
-        <v>1918100</v>
+        <v>2410000</v>
       </c>
       <c r="I66" s="3">
-        <v>1278500</v>
+        <v>1912800</v>
       </c>
       <c r="J66" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="K66" s="3">
         <v>561300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2899,17 +3066,17 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>160300</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>151700</v>
+        <v>159900</v>
       </c>
       <c r="J70" s="3">
+        <v>151300</v>
+      </c>
+      <c r="K70" s="3">
         <v>42200</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,36 +3128,39 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>907500</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>532300</v>
+        <v>905000</v>
       </c>
       <c r="F72" s="3">
-        <v>172100</v>
+        <v>530900</v>
       </c>
       <c r="G72" s="3">
+        <v>171600</v>
+      </c>
+      <c r="H72" s="3">
         <v>2100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-19100</v>
-      </c>
       <c r="I72" s="3">
-        <v>-29600</v>
+        <v>-19000</v>
       </c>
       <c r="J72" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-24000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,36 +3296,39 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>2674200</v>
+      <c r="D76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E76" s="3">
-        <v>2690100</v>
+        <v>2666900</v>
       </c>
       <c r="F76" s="3">
-        <v>1065000</v>
+        <v>2682800</v>
       </c>
       <c r="G76" s="3">
-        <v>326700</v>
+        <v>1062100</v>
       </c>
       <c r="H76" s="3">
-        <v>-19300</v>
+        <v>325800</v>
       </c>
       <c r="I76" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="J76" s="3">
         <v>-29800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-24400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,41 +3380,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,36 +3427,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>375200</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>360200</v>
+        <v>374200</v>
       </c>
       <c r="F81" s="3">
-        <v>169900</v>
+        <v>359300</v>
       </c>
       <c r="G81" s="3">
-        <v>18400</v>
+        <v>169500</v>
       </c>
       <c r="H81" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I81" s="3">
         <v>4700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-7200</v>
-      </c>
       <c r="J81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-14900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,8 +3490,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3314,13 +3512,13 @@
         <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>500</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,36 +3739,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>445500</v>
+        <v>444200</v>
       </c>
       <c r="E89" s="3">
-        <v>770700</v>
+        <v>768600</v>
       </c>
       <c r="F89" s="3">
-        <v>2622300</v>
+        <v>2615200</v>
       </c>
       <c r="G89" s="3">
-        <v>252500</v>
+        <v>251800</v>
       </c>
       <c r="H89" s="3">
-        <v>573000</v>
+        <v>571500</v>
       </c>
       <c r="I89" s="3">
-        <v>237800</v>
+        <v>237200</v>
       </c>
       <c r="J89" s="3">
+        <v>178700</v>
+      </c>
+      <c r="K89" s="3">
         <v>179200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,8 +3802,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3598,19 +3818,19 @@
         <v>-5700</v>
       </c>
       <c r="G91" s="3">
-        <v>-15200</v>
+        <v>-15100</v>
       </c>
       <c r="H91" s="3">
         <v>-2400</v>
       </c>
       <c r="I91" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>-500</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,9 +3925,12 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3709,10 +3938,10 @@
         <v>12000</v>
       </c>
       <c r="E94" s="3">
-        <v>-123500</v>
+        <v>-123200</v>
       </c>
       <c r="F94" s="3">
-        <v>-31300</v>
+        <v>-31200</v>
       </c>
       <c r="G94" s="3">
         <v>-20500</v>
@@ -3726,8 +3955,8 @@
       <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>-800</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,35 +4153,38 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-898600</v>
+        <v>-896100</v>
       </c>
       <c r="E100" s="3">
-        <v>1352900</v>
+        <v>1349300</v>
       </c>
       <c r="F100" s="3">
-        <v>1077700</v>
+        <v>1074700</v>
       </c>
       <c r="G100" s="3">
-        <v>147600</v>
+        <v>147200</v>
       </c>
       <c r="H100" s="3">
         <v>4600</v>
       </c>
       <c r="I100" s="3">
-        <v>276400</v>
+        <v>275600</v>
       </c>
       <c r="J100" s="3">
         <v>18900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>18900</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
@@ -3950,9 +4195,12 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3977,8 +4225,8 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -3989,36 +4237,39 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-458400</v>
+        <v>-457100</v>
       </c>
       <c r="E102" s="3">
-        <v>2021500</v>
+        <v>2016000</v>
       </c>
       <c r="F102" s="3">
-        <v>3668600</v>
+        <v>3658600</v>
       </c>
       <c r="G102" s="3">
-        <v>373800</v>
+        <v>372800</v>
       </c>
       <c r="H102" s="3">
-        <v>568600</v>
+        <v>567000</v>
       </c>
       <c r="I102" s="3">
-        <v>516300</v>
+        <v>514900</v>
       </c>
       <c r="J102" s="3">
+        <v>196800</v>
+      </c>
+      <c r="K102" s="3">
         <v>197300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1279500</v>
+        <v>1281600</v>
       </c>
       <c r="E8" s="3">
-        <v>973400</v>
+        <v>975000</v>
       </c>
       <c r="F8" s="3">
-        <v>909600</v>
+        <v>911100</v>
       </c>
       <c r="G8" s="3">
-        <v>423300</v>
+        <v>424000</v>
       </c>
       <c r="H8" s="3">
-        <v>135700</v>
+        <v>135900</v>
       </c>
       <c r="I8" s="3">
-        <v>103700</v>
+        <v>103900</v>
       </c>
       <c r="J8" s="3">
-        <v>39800</v>
+        <v>39900</v>
       </c>
       <c r="K8" s="3">
         <v>11200</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>196400</v>
+        <v>196700</v>
       </c>
       <c r="E9" s="3">
-        <v>127300</v>
+        <v>127600</v>
       </c>
       <c r="F9" s="3">
-        <v>154200</v>
+        <v>154400</v>
       </c>
       <c r="G9" s="3">
-        <v>89000</v>
+        <v>89100</v>
       </c>
       <c r="H9" s="3">
-        <v>36000</v>
+        <v>36100</v>
       </c>
       <c r="I9" s="3">
-        <v>31900</v>
+        <v>32000</v>
       </c>
       <c r="J9" s="3">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="K9" s="3">
         <v>5800</v>
@@ -808,22 +808,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1083100</v>
+        <v>1084900</v>
       </c>
       <c r="E10" s="3">
-        <v>846000</v>
+        <v>847400</v>
       </c>
       <c r="F10" s="3">
-        <v>755400</v>
+        <v>756700</v>
       </c>
       <c r="G10" s="3">
-        <v>334300</v>
+        <v>334800</v>
       </c>
       <c r="H10" s="3">
-        <v>99700</v>
+        <v>99900</v>
       </c>
       <c r="I10" s="3">
-        <v>71800</v>
+        <v>71900</v>
       </c>
       <c r="J10" s="3">
         <v>25900</v>
@@ -868,19 +868,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>184200</v>
+        <v>184500</v>
       </c>
       <c r="E12" s="3">
-        <v>156200</v>
+        <v>156500</v>
       </c>
       <c r="F12" s="3">
-        <v>103000</v>
+        <v>103100</v>
       </c>
       <c r="G12" s="3">
-        <v>65600</v>
+        <v>65700</v>
       </c>
       <c r="H12" s="3">
-        <v>33500</v>
+        <v>33600</v>
       </c>
       <c r="I12" s="3">
         <v>19300</v>
@@ -1050,23 +1050,23 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>640400</v>
       </c>
       <c r="E17" s="3">
-        <v>517100</v>
+        <v>518000</v>
       </c>
       <c r="F17" s="3">
-        <v>502700</v>
+        <v>503600</v>
       </c>
       <c r="G17" s="3">
-        <v>235600</v>
+        <v>236000</v>
       </c>
       <c r="H17" s="3">
-        <v>111700</v>
+        <v>111900</v>
       </c>
       <c r="I17" s="3">
-        <v>77000</v>
+        <v>77200</v>
       </c>
       <c r="J17" s="3">
         <v>38800</v>
@@ -1092,20 +1092,20 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>641200</v>
       </c>
       <c r="E18" s="3">
-        <v>456200</v>
+        <v>457000</v>
       </c>
       <c r="F18" s="3">
-        <v>406900</v>
+        <v>407600</v>
       </c>
       <c r="G18" s="3">
-        <v>187700</v>
+        <v>188000</v>
       </c>
       <c r="H18" s="3">
-        <v>24000</v>
+        <v>24100</v>
       </c>
       <c r="I18" s="3">
         <v>26700</v>
@@ -1152,8 +1152,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>4300</v>
       </c>
       <c r="E20" s="3">
         <v>-26900</v>
@@ -1194,26 +1194,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>653300</v>
       </c>
       <c r="E21" s="3">
-        <v>434000</v>
+        <v>437100</v>
       </c>
       <c r="F21" s="3">
-        <v>410700</v>
+        <v>412500</v>
       </c>
       <c r="G21" s="3">
-        <v>187500</v>
+        <v>189200</v>
       </c>
       <c r="H21" s="3">
-        <v>23800</v>
+        <v>24900</v>
       </c>
       <c r="I21" s="3">
-        <v>26200</v>
+        <v>26800</v>
       </c>
       <c r="J21" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K21" s="3">
         <v>-13900</v>
@@ -1279,19 +1279,19 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>644400</v>
+        <v>645500</v>
       </c>
       <c r="E23" s="3">
-        <v>429400</v>
+        <v>430100</v>
       </c>
       <c r="F23" s="3">
-        <v>407200</v>
+        <v>407900</v>
       </c>
       <c r="G23" s="3">
-        <v>185400</v>
+        <v>185700</v>
       </c>
       <c r="H23" s="3">
-        <v>22700</v>
+        <v>22800</v>
       </c>
       <c r="I23" s="3">
         <v>25700</v>
@@ -1321,10 +1321,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>95700</v>
+        <v>95800</v>
       </c>
       <c r="E24" s="3">
-        <v>52900</v>
+        <v>53000</v>
       </c>
       <c r="F24" s="3">
         <v>48000</v>
@@ -1404,17 +1404,17 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>549600</v>
       </c>
       <c r="E26" s="3">
-        <v>376400</v>
+        <v>377100</v>
       </c>
       <c r="F26" s="3">
-        <v>359300</v>
+        <v>359800</v>
       </c>
       <c r="G26" s="3">
-        <v>169500</v>
+        <v>169700</v>
       </c>
       <c r="H26" s="3">
         <v>21200</v>
@@ -1446,17 +1446,17 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>548200</v>
       </c>
       <c r="E27" s="3">
-        <v>374200</v>
+        <v>374800</v>
       </c>
       <c r="F27" s="3">
-        <v>359300</v>
+        <v>359800</v>
       </c>
       <c r="G27" s="3">
-        <v>169500</v>
+        <v>169700</v>
       </c>
       <c r="H27" s="3">
         <v>18300</v>
@@ -1656,8 +1656,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-4300</v>
       </c>
       <c r="E32" s="3">
         <v>26900</v>
@@ -1698,17 +1698,17 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>548200</v>
       </c>
       <c r="E33" s="3">
-        <v>374200</v>
+        <v>374800</v>
       </c>
       <c r="F33" s="3">
-        <v>359300</v>
+        <v>359800</v>
       </c>
       <c r="G33" s="3">
-        <v>169500</v>
+        <v>169700</v>
       </c>
       <c r="H33" s="3">
         <v>18300</v>
@@ -1782,17 +1782,17 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>548200</v>
       </c>
       <c r="E35" s="3">
-        <v>374200</v>
+        <v>374800</v>
       </c>
       <c r="F35" s="3">
-        <v>359300</v>
+        <v>359800</v>
       </c>
       <c r="G35" s="3">
-        <v>169500</v>
+        <v>169700</v>
       </c>
       <c r="H35" s="3">
         <v>18300</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6303400</v>
+        <v>6313700</v>
       </c>
       <c r="E41" s="3">
-        <v>7122500</v>
+        <v>7134200</v>
       </c>
       <c r="F41" s="3">
-        <v>7579600</v>
+        <v>7592000</v>
       </c>
       <c r="G41" s="3">
-        <v>5563800</v>
+        <v>5573000</v>
       </c>
       <c r="H41" s="3">
-        <v>1905300</v>
+        <v>1908400</v>
       </c>
       <c r="I41" s="3">
-        <v>1532400</v>
+        <v>1534900</v>
       </c>
       <c r="J41" s="3">
-        <v>965400</v>
+        <v>967000</v>
       </c>
       <c r="K41" s="3">
         <v>451800</v>
@@ -1950,13 +1950,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>415900</v>
+        <v>416600</v>
       </c>
       <c r="E42" s="3">
-        <v>91100</v>
+        <v>91300</v>
       </c>
       <c r="F42" s="3">
-        <v>163100</v>
+        <v>163400</v>
       </c>
       <c r="G42" s="3">
         <v>38400</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5455700</v>
+        <v>5464700</v>
       </c>
       <c r="E43" s="3">
-        <v>4669200</v>
+        <v>4676900</v>
       </c>
       <c r="F43" s="3">
-        <v>5121500</v>
+        <v>5129900</v>
       </c>
       <c r="G43" s="3">
-        <v>1037200</v>
+        <v>1038900</v>
       </c>
       <c r="H43" s="3">
-        <v>237300</v>
+        <v>237700</v>
       </c>
       <c r="I43" s="3">
-        <v>107000</v>
+        <v>107100</v>
       </c>
       <c r="J43" s="3">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="K43" s="3">
         <v>104400</v>
@@ -2082,7 +2082,7 @@
         <v>14500</v>
       </c>
       <c r="F45" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G45" s="3">
         <v>1500</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12199500</v>
+        <v>12219500</v>
       </c>
       <c r="E46" s="3">
-        <v>11897300</v>
+        <v>11916900</v>
       </c>
       <c r="F46" s="3">
-        <v>12873800</v>
+        <v>12894900</v>
       </c>
       <c r="G46" s="3">
-        <v>6640900</v>
+        <v>6651800</v>
       </c>
       <c r="H46" s="3">
-        <v>2156100</v>
+        <v>2159700</v>
       </c>
       <c r="I46" s="3">
-        <v>1648100</v>
+        <v>1650800</v>
       </c>
       <c r="J46" s="3">
-        <v>1017000</v>
+        <v>1018700</v>
       </c>
       <c r="K46" s="3">
         <v>556800</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>32900</v>
+        <v>33000</v>
       </c>
       <c r="E47" s="3">
-        <v>35300</v>
+        <v>35400</v>
       </c>
       <c r="F47" s="3">
         <v>3000</v>
       </c>
       <c r="G47" s="3">
-        <v>2406600</v>
+        <v>2410600</v>
       </c>
       <c r="H47" s="3">
-        <v>536300</v>
+        <v>537200</v>
       </c>
       <c r="I47" s="3">
-        <v>394600</v>
+        <v>395300</v>
       </c>
       <c r="J47" s="3">
-        <v>371800</v>
+        <v>372400</v>
       </c>
       <c r="K47" s="3">
         <v>16900</v>
@@ -2202,19 +2202,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>28600</v>
+        <v>44700</v>
       </c>
       <c r="E48" s="3">
-        <v>43800</v>
+        <v>43900</v>
       </c>
       <c r="F48" s="3">
-        <v>53600</v>
+        <v>53700</v>
       </c>
       <c r="G48" s="3">
-        <v>40500</v>
+        <v>40600</v>
       </c>
       <c r="H48" s="3">
-        <v>35700</v>
+        <v>35800</v>
       </c>
       <c r="I48" s="3">
         <v>2900</v>
@@ -2243,8 +2243,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>9200</v>
       </c>
       <c r="E49" s="3">
         <v>7000</v>
@@ -2370,13 +2370,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>156800</v>
+        <v>131900</v>
       </c>
       <c r="E52" s="3">
-        <v>97800</v>
+        <v>97900</v>
       </c>
       <c r="F52" s="3">
-        <v>48000</v>
+        <v>48100</v>
       </c>
       <c r="G52" s="3">
         <v>30500</v>
@@ -2385,7 +2385,7 @@
         <v>6700</v>
       </c>
       <c r="I52" s="3">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="J52" s="3">
         <v>5900</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12417800</v>
+        <v>12438200</v>
       </c>
       <c r="E54" s="3">
-        <v>12081200</v>
+        <v>12101100</v>
       </c>
       <c r="F54" s="3">
-        <v>12980700</v>
+        <v>13002000</v>
       </c>
       <c r="G54" s="3">
-        <v>9119800</v>
+        <v>9134800</v>
       </c>
       <c r="H54" s="3">
-        <v>2735800</v>
+        <v>2740300</v>
       </c>
       <c r="I54" s="3">
-        <v>2053500</v>
+        <v>2056900</v>
       </c>
       <c r="J54" s="3">
-        <v>1396500</v>
+        <v>1398800</v>
       </c>
       <c r="K54" s="3">
         <v>579100</v>
@@ -2531,26 +2531,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>8250900</v>
       </c>
       <c r="E57" s="3">
-        <v>8830700</v>
+        <v>8845200</v>
       </c>
       <c r="F57" s="3">
-        <v>8580700</v>
+        <v>8594800</v>
       </c>
       <c r="G57" s="3">
-        <v>6509700</v>
+        <v>6520400</v>
       </c>
       <c r="H57" s="3">
-        <v>2163500</v>
+        <v>2167000</v>
       </c>
       <c r="I57" s="3">
-        <v>1690800</v>
+        <v>1693500</v>
       </c>
       <c r="J57" s="3">
-        <v>1067900</v>
+        <v>1069700</v>
       </c>
       <c r="K57" s="3">
         <v>531900</v>
@@ -2573,26 +2573,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>723700</v>
       </c>
       <c r="E58" s="3">
-        <v>317100</v>
+        <v>317600</v>
       </c>
       <c r="F58" s="3">
-        <v>1383900</v>
+        <v>1386200</v>
       </c>
       <c r="G58" s="3">
-        <v>1398000</v>
+        <v>1400300</v>
       </c>
       <c r="H58" s="3">
-        <v>187800</v>
+        <v>188100</v>
       </c>
       <c r="I58" s="3">
-        <v>201500</v>
+        <v>201800</v>
       </c>
       <c r="J58" s="3">
-        <v>197200</v>
+        <v>197500</v>
       </c>
       <c r="K58" s="3">
         <v>20700</v>
@@ -2615,20 +2615,20 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>299900</v>
       </c>
       <c r="E59" s="3">
-        <v>251700</v>
+        <v>252100</v>
       </c>
       <c r="F59" s="3">
-        <v>311000</v>
+        <v>311500</v>
       </c>
       <c r="G59" s="3">
-        <v>121600</v>
+        <v>121800</v>
       </c>
       <c r="H59" s="3">
-        <v>36600</v>
+        <v>36700</v>
       </c>
       <c r="I59" s="3">
         <v>20600</v>
@@ -2657,26 +2657,26 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>9274500</v>
       </c>
       <c r="E60" s="3">
-        <v>9399500</v>
+        <v>9415000</v>
       </c>
       <c r="F60" s="3">
-        <v>10275600</v>
+        <v>10292400</v>
       </c>
       <c r="G60" s="3">
-        <v>8029400</v>
+        <v>8042500</v>
       </c>
       <c r="H60" s="3">
-        <v>2387900</v>
+        <v>2391800</v>
       </c>
       <c r="I60" s="3">
-        <v>1912800</v>
+        <v>1916000</v>
       </c>
       <c r="J60" s="3">
-        <v>1275000</v>
+        <v>1277100</v>
       </c>
       <c r="K60" s="3">
         <v>557200</v>
@@ -2741,20 +2741,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>17400</v>
       </c>
       <c r="E62" s="3">
-        <v>14700</v>
+        <v>14800</v>
       </c>
       <c r="F62" s="3">
-        <v>22300</v>
+        <v>22400</v>
       </c>
       <c r="G62" s="3">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="H62" s="3">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2909,26 +2909,26 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>9292200</v>
       </c>
       <c r="E66" s="3">
-        <v>9414300</v>
+        <v>9429800</v>
       </c>
       <c r="F66" s="3">
-        <v>10297900</v>
+        <v>10314800</v>
       </c>
       <c r="G66" s="3">
-        <v>8057800</v>
+        <v>8071000</v>
       </c>
       <c r="H66" s="3">
-        <v>2410000</v>
+        <v>2413900</v>
       </c>
       <c r="I66" s="3">
-        <v>1912800</v>
+        <v>1916000</v>
       </c>
       <c r="J66" s="3">
-        <v>1275000</v>
+        <v>1277100</v>
       </c>
       <c r="K66" s="3">
         <v>561300</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>159900</v>
+        <v>160100</v>
       </c>
       <c r="J70" s="3">
-        <v>151300</v>
+        <v>151500</v>
       </c>
       <c r="K70" s="3">
         <v>42200</v>
@@ -3137,26 +3137,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>1454800</v>
       </c>
       <c r="E72" s="3">
-        <v>905000</v>
+        <v>906500</v>
       </c>
       <c r="F72" s="3">
-        <v>530900</v>
+        <v>531700</v>
       </c>
       <c r="G72" s="3">
-        <v>171600</v>
+        <v>171900</v>
       </c>
       <c r="H72" s="3">
         <v>2100</v>
       </c>
       <c r="I72" s="3">
-        <v>-19000</v>
+        <v>-19100</v>
       </c>
       <c r="J72" s="3">
-        <v>-29500</v>
+        <v>-29600</v>
       </c>
       <c r="K72" s="3">
         <v>-24000</v>
@@ -3305,20 +3305,20 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>3146000</v>
       </c>
       <c r="E76" s="3">
-        <v>2666900</v>
+        <v>2671300</v>
       </c>
       <c r="F76" s="3">
-        <v>2682800</v>
+        <v>2687200</v>
       </c>
       <c r="G76" s="3">
-        <v>1062100</v>
+        <v>1063800</v>
       </c>
       <c r="H76" s="3">
-        <v>325800</v>
+        <v>326300</v>
       </c>
       <c r="I76" s="3">
         <v>-19200</v>
@@ -3436,17 +3436,17 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>548200</v>
       </c>
       <c r="E81" s="3">
-        <v>374200</v>
+        <v>374800</v>
       </c>
       <c r="F81" s="3">
-        <v>359300</v>
+        <v>359800</v>
       </c>
       <c r="G81" s="3">
-        <v>169500</v>
+        <v>169700</v>
       </c>
       <c r="H81" s="3">
         <v>18300</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E83" s="3">
         <v>7000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
-        <v>500</v>
-      </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>444200</v>
+        <v>-811500</v>
       </c>
       <c r="E89" s="3">
-        <v>768600</v>
+        <v>445000</v>
       </c>
       <c r="F89" s="3">
-        <v>2615200</v>
+        <v>769800</v>
       </c>
       <c r="G89" s="3">
-        <v>251800</v>
+        <v>2619500</v>
       </c>
       <c r="H89" s="3">
-        <v>571500</v>
+        <v>252200</v>
       </c>
       <c r="I89" s="3">
-        <v>237200</v>
+        <v>572400</v>
       </c>
       <c r="J89" s="3">
-        <v>178700</v>
+        <v>237600</v>
       </c>
       <c r="K89" s="3">
         <v>179200</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-15100</v>
-      </c>
       <c r="H91" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-500</v>
       </c>
       <c r="K91" s="3">
         <v>-500</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-313000</v>
+      </c>
+      <c r="E94" s="3">
         <v>12000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-123200</v>
-      </c>
       <c r="F94" s="3">
-        <v>-31200</v>
+        <v>-123400</v>
       </c>
       <c r="G94" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-20500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-800</v>
       </c>
       <c r="K94" s="3">
         <v>-800</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-896100</v>
+        <v>295500</v>
       </c>
       <c r="E100" s="3">
-        <v>1349300</v>
+        <v>-897600</v>
       </c>
       <c r="F100" s="3">
-        <v>1074700</v>
+        <v>1351500</v>
       </c>
       <c r="G100" s="3">
-        <v>147200</v>
+        <v>1076500</v>
       </c>
       <c r="H100" s="3">
+        <v>147500</v>
+      </c>
+      <c r="I100" s="3">
         <v>4600</v>
       </c>
-      <c r="I100" s="3">
-        <v>275600</v>
-      </c>
       <c r="J100" s="3">
-        <v>18900</v>
+        <v>276100</v>
       </c>
       <c r="K100" s="3">
         <v>18900</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-17300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>21400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-457100</v>
+        <v>-820500</v>
       </c>
       <c r="E102" s="3">
-        <v>2016000</v>
+        <v>-457900</v>
       </c>
       <c r="F102" s="3">
-        <v>3658600</v>
+        <v>2019300</v>
       </c>
       <c r="G102" s="3">
-        <v>372800</v>
+        <v>3664600</v>
       </c>
       <c r="H102" s="3">
-        <v>567000</v>
+        <v>373400</v>
       </c>
       <c r="I102" s="3">
-        <v>514900</v>
+        <v>567900</v>
       </c>
       <c r="J102" s="3">
-        <v>196800</v>
+        <v>515700</v>
       </c>
       <c r="K102" s="3">
         <v>197300</v>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1281600</v>
+        <v>1283400</v>
       </c>
       <c r="E8" s="3">
-        <v>975000</v>
+        <v>976300</v>
       </c>
       <c r="F8" s="3">
-        <v>911100</v>
+        <v>912400</v>
       </c>
       <c r="G8" s="3">
-        <v>424000</v>
+        <v>424500</v>
       </c>
       <c r="H8" s="3">
-        <v>135900</v>
+        <v>136100</v>
       </c>
       <c r="I8" s="3">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="J8" s="3">
-        <v>39900</v>
+        <v>40000</v>
       </c>
       <c r="K8" s="3">
         <v>11200</v>
@@ -766,16 +766,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>196700</v>
+        <v>197000</v>
       </c>
       <c r="E9" s="3">
-        <v>127600</v>
+        <v>127700</v>
       </c>
       <c r="F9" s="3">
-        <v>154400</v>
+        <v>154700</v>
       </c>
       <c r="G9" s="3">
-        <v>89100</v>
+        <v>89200</v>
       </c>
       <c r="H9" s="3">
         <v>36100</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1084900</v>
+        <v>1086400</v>
       </c>
       <c r="E10" s="3">
-        <v>847400</v>
+        <v>848600</v>
       </c>
       <c r="F10" s="3">
-        <v>756700</v>
+        <v>757700</v>
       </c>
       <c r="G10" s="3">
-        <v>334800</v>
+        <v>335300</v>
       </c>
       <c r="H10" s="3">
-        <v>99900</v>
+        <v>100000</v>
       </c>
       <c r="I10" s="3">
-        <v>71900</v>
+        <v>72000</v>
       </c>
       <c r="J10" s="3">
-        <v>25900</v>
+        <v>26000</v>
       </c>
       <c r="K10" s="3">
         <v>5400</v>
@@ -868,22 +868,22 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>184500</v>
+        <v>184800</v>
       </c>
       <c r="E12" s="3">
-        <v>156500</v>
+        <v>156700</v>
       </c>
       <c r="F12" s="3">
-        <v>103100</v>
+        <v>103300</v>
       </c>
       <c r="G12" s="3">
-        <v>65700</v>
+        <v>65800</v>
       </c>
       <c r="H12" s="3">
         <v>33600</v>
       </c>
       <c r="I12" s="3">
-        <v>19300</v>
+        <v>19400</v>
       </c>
       <c r="J12" s="3">
         <v>12200</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>640400</v>
+        <v>641300</v>
       </c>
       <c r="E17" s="3">
-        <v>518000</v>
+        <v>518700</v>
       </c>
       <c r="F17" s="3">
-        <v>503600</v>
+        <v>504300</v>
       </c>
       <c r="G17" s="3">
-        <v>236000</v>
+        <v>236300</v>
       </c>
       <c r="H17" s="3">
-        <v>111900</v>
+        <v>112000</v>
       </c>
       <c r="I17" s="3">
-        <v>77200</v>
+        <v>77300</v>
       </c>
       <c r="J17" s="3">
-        <v>38800</v>
+        <v>38900</v>
       </c>
       <c r="K17" s="3">
         <v>25300</v>
@@ -1093,22 +1093,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>641200</v>
+        <v>642100</v>
       </c>
       <c r="E18" s="3">
-        <v>457000</v>
+        <v>457600</v>
       </c>
       <c r="F18" s="3">
-        <v>407600</v>
+        <v>408100</v>
       </c>
       <c r="G18" s="3">
-        <v>188000</v>
+        <v>188200</v>
       </c>
       <c r="H18" s="3">
         <v>24100</v>
       </c>
       <c r="I18" s="3">
-        <v>26700</v>
+        <v>26800</v>
       </c>
       <c r="J18" s="3">
         <v>1100</v>
@@ -1156,7 +1156,7 @@
         <v>4300</v>
       </c>
       <c r="E20" s="3">
-        <v>-26900</v>
+        <v>-27000</v>
       </c>
       <c r="F20" s="3">
         <v>300</v>
@@ -1195,16 +1195,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>653300</v>
+        <v>654200</v>
       </c>
       <c r="E21" s="3">
-        <v>437100</v>
+        <v>437700</v>
       </c>
       <c r="F21" s="3">
-        <v>412500</v>
+        <v>413100</v>
       </c>
       <c r="G21" s="3">
-        <v>189200</v>
+        <v>189500</v>
       </c>
       <c r="H21" s="3">
         <v>24900</v>
@@ -1279,16 +1279,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>645500</v>
+        <v>646400</v>
       </c>
       <c r="E23" s="3">
-        <v>430100</v>
+        <v>430700</v>
       </c>
       <c r="F23" s="3">
-        <v>407900</v>
+        <v>408400</v>
       </c>
       <c r="G23" s="3">
-        <v>185700</v>
+        <v>186000</v>
       </c>
       <c r="H23" s="3">
         <v>22800</v>
@@ -1321,13 +1321,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>95800</v>
+        <v>96000</v>
       </c>
       <c r="E24" s="3">
-        <v>53000</v>
+        <v>53100</v>
       </c>
       <c r="F24" s="3">
-        <v>48000</v>
+        <v>48100</v>
       </c>
       <c r="G24" s="3">
         <v>16000</v>
@@ -1405,22 +1405,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>549600</v>
+        <v>550400</v>
       </c>
       <c r="E26" s="3">
-        <v>377100</v>
+        <v>377600</v>
       </c>
       <c r="F26" s="3">
-        <v>359800</v>
+        <v>360400</v>
       </c>
       <c r="G26" s="3">
-        <v>169700</v>
+        <v>170000</v>
       </c>
       <c r="H26" s="3">
         <v>21200</v>
       </c>
       <c r="I26" s="3">
-        <v>17700</v>
+        <v>17800</v>
       </c>
       <c r="J26" s="3">
         <v>-1000</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>548200</v>
+        <v>549000</v>
       </c>
       <c r="E27" s="3">
-        <v>374800</v>
+        <v>375300</v>
       </c>
       <c r="F27" s="3">
-        <v>359800</v>
+        <v>360400</v>
       </c>
       <c r="G27" s="3">
-        <v>169700</v>
+        <v>170000</v>
       </c>
       <c r="H27" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="I27" s="3">
         <v>4700</v>
       </c>
       <c r="J27" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="K27" s="3">
         <v>-14900</v>
@@ -1660,7 +1660,7 @@
         <v>-4300</v>
       </c>
       <c r="E32" s="3">
-        <v>26900</v>
+        <v>27000</v>
       </c>
       <c r="F32" s="3">
         <v>-300</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>548200</v>
+        <v>549000</v>
       </c>
       <c r="E33" s="3">
-        <v>374800</v>
+        <v>375300</v>
       </c>
       <c r="F33" s="3">
-        <v>359800</v>
+        <v>360400</v>
       </c>
       <c r="G33" s="3">
-        <v>169700</v>
+        <v>170000</v>
       </c>
       <c r="H33" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="I33" s="3">
         <v>4700</v>
       </c>
       <c r="J33" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="K33" s="3">
         <v>-14900</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>548200</v>
+        <v>549000</v>
       </c>
       <c r="E35" s="3">
-        <v>374800</v>
+        <v>375300</v>
       </c>
       <c r="F35" s="3">
-        <v>359800</v>
+        <v>360400</v>
       </c>
       <c r="G35" s="3">
-        <v>169700</v>
+        <v>170000</v>
       </c>
       <c r="H35" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="I35" s="3">
         <v>4700</v>
       </c>
       <c r="J35" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="K35" s="3">
         <v>-14900</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6313700</v>
+        <v>6322600</v>
       </c>
       <c r="E41" s="3">
-        <v>7134200</v>
+        <v>7144300</v>
       </c>
       <c r="F41" s="3">
-        <v>7592000</v>
+        <v>7602700</v>
       </c>
       <c r="G41" s="3">
-        <v>5573000</v>
+        <v>5580800</v>
       </c>
       <c r="H41" s="3">
-        <v>1908400</v>
+        <v>1911100</v>
       </c>
       <c r="I41" s="3">
-        <v>1534900</v>
+        <v>1537100</v>
       </c>
       <c r="J41" s="3">
-        <v>967000</v>
+        <v>968400</v>
       </c>
       <c r="K41" s="3">
         <v>451800</v>
@@ -1950,16 +1950,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>416600</v>
+        <v>417200</v>
       </c>
       <c r="E42" s="3">
-        <v>91300</v>
+        <v>91400</v>
       </c>
       <c r="F42" s="3">
-        <v>163400</v>
+        <v>163600</v>
       </c>
       <c r="G42" s="3">
-        <v>38400</v>
+        <v>38500</v>
       </c>
       <c r="H42" s="3">
         <v>12000</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5464700</v>
+        <v>5472400</v>
       </c>
       <c r="E43" s="3">
-        <v>4676900</v>
+        <v>4683400</v>
       </c>
       <c r="F43" s="3">
-        <v>5129900</v>
+        <v>5137100</v>
       </c>
       <c r="G43" s="3">
-        <v>1038900</v>
+        <v>1040400</v>
       </c>
       <c r="H43" s="3">
-        <v>237700</v>
+        <v>238000</v>
       </c>
       <c r="I43" s="3">
-        <v>107100</v>
+        <v>107300</v>
       </c>
       <c r="J43" s="3">
-        <v>51200</v>
+        <v>51300</v>
       </c>
       <c r="K43" s="3">
         <v>104400</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12219500</v>
+        <v>12236700</v>
       </c>
       <c r="E46" s="3">
-        <v>11916900</v>
+        <v>11933600</v>
       </c>
       <c r="F46" s="3">
-        <v>12894900</v>
+        <v>12913100</v>
       </c>
       <c r="G46" s="3">
-        <v>6651800</v>
+        <v>6661100</v>
       </c>
       <c r="H46" s="3">
-        <v>2159700</v>
+        <v>2162700</v>
       </c>
       <c r="I46" s="3">
-        <v>1650800</v>
+        <v>1653100</v>
       </c>
       <c r="J46" s="3">
-        <v>1018700</v>
+        <v>1020100</v>
       </c>
       <c r="K46" s="3">
         <v>556800</v>
@@ -2163,22 +2163,22 @@
         <v>33000</v>
       </c>
       <c r="E47" s="3">
-        <v>35400</v>
+        <v>35500</v>
       </c>
       <c r="F47" s="3">
         <v>3000</v>
       </c>
       <c r="G47" s="3">
-        <v>2410600</v>
+        <v>2414000</v>
       </c>
       <c r="H47" s="3">
-        <v>537200</v>
+        <v>537900</v>
       </c>
       <c r="I47" s="3">
-        <v>395300</v>
+        <v>395800</v>
       </c>
       <c r="J47" s="3">
-        <v>372400</v>
+        <v>372900</v>
       </c>
       <c r="K47" s="3">
         <v>16900</v>
@@ -2202,16 +2202,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>44700</v>
+        <v>44800</v>
       </c>
       <c r="E48" s="3">
         <v>43900</v>
       </c>
       <c r="F48" s="3">
-        <v>53700</v>
+        <v>53800</v>
       </c>
       <c r="G48" s="3">
-        <v>40600</v>
+        <v>40700</v>
       </c>
       <c r="H48" s="3">
         <v>35800</v>
@@ -2370,16 +2370,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>131900</v>
+        <v>132000</v>
       </c>
       <c r="E52" s="3">
-        <v>97900</v>
+        <v>98100</v>
       </c>
       <c r="F52" s="3">
-        <v>48100</v>
+        <v>48200</v>
       </c>
       <c r="G52" s="3">
-        <v>30500</v>
+        <v>30600</v>
       </c>
       <c r="H52" s="3">
         <v>6700</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12438200</v>
+        <v>12455700</v>
       </c>
       <c r="E54" s="3">
-        <v>12101100</v>
+        <v>12118100</v>
       </c>
       <c r="F54" s="3">
-        <v>13002000</v>
+        <v>13020300</v>
       </c>
       <c r="G54" s="3">
-        <v>9134800</v>
+        <v>9147600</v>
       </c>
       <c r="H54" s="3">
-        <v>2740300</v>
+        <v>2744100</v>
       </c>
       <c r="I54" s="3">
-        <v>2056900</v>
+        <v>2059700</v>
       </c>
       <c r="J54" s="3">
-        <v>1398800</v>
+        <v>1400800</v>
       </c>
       <c r="K54" s="3">
         <v>579100</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8250900</v>
+        <v>8262500</v>
       </c>
       <c r="E57" s="3">
-        <v>8845200</v>
+        <v>8857600</v>
       </c>
       <c r="F57" s="3">
-        <v>8594800</v>
+        <v>8606900</v>
       </c>
       <c r="G57" s="3">
-        <v>6520400</v>
+        <v>6529600</v>
       </c>
       <c r="H57" s="3">
-        <v>2167000</v>
+        <v>2170100</v>
       </c>
       <c r="I57" s="3">
-        <v>1693500</v>
+        <v>1695900</v>
       </c>
       <c r="J57" s="3">
-        <v>1069700</v>
+        <v>1071200</v>
       </c>
       <c r="K57" s="3">
         <v>531900</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>723700</v>
+        <v>724700</v>
       </c>
       <c r="E58" s="3">
-        <v>317600</v>
+        <v>318100</v>
       </c>
       <c r="F58" s="3">
-        <v>1386200</v>
+        <v>1388100</v>
       </c>
       <c r="G58" s="3">
-        <v>1400300</v>
+        <v>1402300</v>
       </c>
       <c r="H58" s="3">
-        <v>188100</v>
+        <v>188400</v>
       </c>
       <c r="I58" s="3">
-        <v>201800</v>
+        <v>202100</v>
       </c>
       <c r="J58" s="3">
-        <v>197500</v>
+        <v>197800</v>
       </c>
       <c r="K58" s="3">
         <v>20700</v>
@@ -2616,19 +2616,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>299900</v>
+        <v>300400</v>
       </c>
       <c r="E59" s="3">
-        <v>252100</v>
+        <v>252500</v>
       </c>
       <c r="F59" s="3">
-        <v>311500</v>
+        <v>311900</v>
       </c>
       <c r="G59" s="3">
-        <v>121800</v>
+        <v>122000</v>
       </c>
       <c r="H59" s="3">
-        <v>36700</v>
+        <v>36800</v>
       </c>
       <c r="I59" s="3">
         <v>20600</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9274500</v>
+        <v>9287500</v>
       </c>
       <c r="E60" s="3">
-        <v>9415000</v>
+        <v>9428200</v>
       </c>
       <c r="F60" s="3">
-        <v>10292400</v>
+        <v>10306900</v>
       </c>
       <c r="G60" s="3">
-        <v>8042500</v>
+        <v>8053900</v>
       </c>
       <c r="H60" s="3">
-        <v>2391800</v>
+        <v>2395200</v>
       </c>
       <c r="I60" s="3">
-        <v>1916000</v>
+        <v>1918700</v>
       </c>
       <c r="J60" s="3">
-        <v>1277100</v>
+        <v>1278900</v>
       </c>
       <c r="K60" s="3">
         <v>557200</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9292200</v>
+        <v>9305300</v>
       </c>
       <c r="E66" s="3">
-        <v>9429800</v>
+        <v>9443000</v>
       </c>
       <c r="F66" s="3">
-        <v>10314800</v>
+        <v>10329300</v>
       </c>
       <c r="G66" s="3">
-        <v>8071000</v>
+        <v>8082300</v>
       </c>
       <c r="H66" s="3">
-        <v>2413900</v>
+        <v>2417300</v>
       </c>
       <c r="I66" s="3">
-        <v>1916000</v>
+        <v>1918700</v>
       </c>
       <c r="J66" s="3">
-        <v>1277100</v>
+        <v>1278900</v>
       </c>
       <c r="K66" s="3">
         <v>561300</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>160100</v>
+        <v>160300</v>
       </c>
       <c r="J70" s="3">
-        <v>151500</v>
+        <v>151800</v>
       </c>
       <c r="K70" s="3">
         <v>42200</v>
@@ -3138,16 +3138,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1454800</v>
+        <v>1456800</v>
       </c>
       <c r="E72" s="3">
-        <v>906500</v>
+        <v>907800</v>
       </c>
       <c r="F72" s="3">
-        <v>531700</v>
+        <v>532500</v>
       </c>
       <c r="G72" s="3">
-        <v>171900</v>
+        <v>172100</v>
       </c>
       <c r="H72" s="3">
         <v>2100</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3146000</v>
+        <v>3150400</v>
       </c>
       <c r="E76" s="3">
-        <v>2671300</v>
+        <v>2675100</v>
       </c>
       <c r="F76" s="3">
-        <v>2687200</v>
+        <v>2691000</v>
       </c>
       <c r="G76" s="3">
-        <v>1063800</v>
+        <v>1065300</v>
       </c>
       <c r="H76" s="3">
-        <v>326300</v>
+        <v>326800</v>
       </c>
       <c r="I76" s="3">
         <v>-19200</v>
       </c>
       <c r="J76" s="3">
-        <v>-29800</v>
+        <v>-29900</v>
       </c>
       <c r="K76" s="3">
         <v>-24400</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>548200</v>
+        <v>549000</v>
       </c>
       <c r="E81" s="3">
-        <v>374800</v>
+        <v>375300</v>
       </c>
       <c r="F81" s="3">
-        <v>359800</v>
+        <v>360400</v>
       </c>
       <c r="G81" s="3">
-        <v>169700</v>
+        <v>170000</v>
       </c>
       <c r="H81" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="I81" s="3">
         <v>4700</v>
       </c>
       <c r="J81" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="K81" s="3">
         <v>-14900</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-811500</v>
+        <v>-812600</v>
       </c>
       <c r="E89" s="3">
-        <v>445000</v>
+        <v>445600</v>
       </c>
       <c r="F89" s="3">
-        <v>769800</v>
+        <v>770900</v>
       </c>
       <c r="G89" s="3">
-        <v>2619500</v>
+        <v>2623200</v>
       </c>
       <c r="H89" s="3">
-        <v>252200</v>
+        <v>252500</v>
       </c>
       <c r="I89" s="3">
-        <v>572400</v>
+        <v>573200</v>
       </c>
       <c r="J89" s="3">
-        <v>237600</v>
+        <v>237900</v>
       </c>
       <c r="K89" s="3">
         <v>179200</v>
@@ -3827,7 +3827,7 @@
         <v>-2400</v>
       </c>
       <c r="J91" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="K91" s="3">
         <v>-500</v>
@@ -3935,13 +3935,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-313000</v>
+        <v>-313400</v>
       </c>
       <c r="E94" s="3">
         <v>12000</v>
       </c>
       <c r="F94" s="3">
-        <v>-123400</v>
+        <v>-123600</v>
       </c>
       <c r="G94" s="3">
         <v>-31300</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>295500</v>
+        <v>295900</v>
       </c>
       <c r="E100" s="3">
-        <v>-897600</v>
+        <v>-898800</v>
       </c>
       <c r="F100" s="3">
-        <v>1351500</v>
+        <v>1353400</v>
       </c>
       <c r="G100" s="3">
-        <v>1076500</v>
+        <v>1078000</v>
       </c>
       <c r="H100" s="3">
-        <v>147500</v>
+        <v>147700</v>
       </c>
       <c r="I100" s="3">
         <v>4600</v>
       </c>
       <c r="J100" s="3">
-        <v>276100</v>
+        <v>276400</v>
       </c>
       <c r="K100" s="3">
         <v>18900</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-820500</v>
+        <v>-821600</v>
       </c>
       <c r="E102" s="3">
-        <v>-457900</v>
+        <v>-458500</v>
       </c>
       <c r="F102" s="3">
-        <v>2019300</v>
+        <v>2022200</v>
       </c>
       <c r="G102" s="3">
-        <v>3664600</v>
+        <v>3669700</v>
       </c>
       <c r="H102" s="3">
-        <v>373400</v>
+        <v>374000</v>
       </c>
       <c r="I102" s="3">
-        <v>567900</v>
+        <v>568700</v>
       </c>
       <c r="J102" s="3">
-        <v>515700</v>
+        <v>516500</v>
       </c>
       <c r="K102" s="3">
         <v>197300</v>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1283400</v>
+        <v>1164600</v>
       </c>
       <c r="E8" s="3">
-        <v>976300</v>
+        <v>939000</v>
       </c>
       <c r="F8" s="3">
-        <v>912400</v>
+        <v>864200</v>
       </c>
       <c r="G8" s="3">
-        <v>424500</v>
+        <v>403100</v>
       </c>
       <c r="H8" s="3">
-        <v>136100</v>
+        <v>124800</v>
       </c>
       <c r="I8" s="3">
-        <v>104000</v>
+        <v>91400</v>
       </c>
       <c r="J8" s="3">
-        <v>40000</v>
+        <v>37300</v>
       </c>
       <c r="K8" s="3">
         <v>11200</v>
@@ -766,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>197000</v>
+        <v>80100</v>
       </c>
       <c r="E9" s="3">
-        <v>127700</v>
+        <v>90200</v>
       </c>
       <c r="F9" s="3">
-        <v>154700</v>
+        <v>106300</v>
       </c>
       <c r="G9" s="3">
-        <v>89200</v>
+        <v>65900</v>
       </c>
       <c r="H9" s="3">
-        <v>36100</v>
+        <v>24700</v>
       </c>
       <c r="I9" s="3">
-        <v>32000</v>
+        <v>19700</v>
       </c>
       <c r="J9" s="3">
-        <v>14000</v>
+        <v>11400</v>
       </c>
       <c r="K9" s="3">
         <v>5800</v>
@@ -808,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1086400</v>
+        <v>1084500</v>
       </c>
       <c r="E10" s="3">
-        <v>848600</v>
+        <v>848700</v>
       </c>
       <c r="F10" s="3">
-        <v>757700</v>
+        <v>757800</v>
       </c>
       <c r="G10" s="3">
-        <v>335300</v>
+        <v>337300</v>
       </c>
       <c r="H10" s="3">
-        <v>100000</v>
+        <v>100100</v>
       </c>
       <c r="I10" s="3">
-        <v>72000</v>
+        <v>71700</v>
       </c>
       <c r="J10" s="3">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="K10" s="3">
         <v>5400</v>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>184800</v>
+        <v>184400</v>
       </c>
       <c r="E12" s="3">
         <v>156700</v>
@@ -877,13 +877,13 @@
         <v>103300</v>
       </c>
       <c r="G12" s="3">
-        <v>65800</v>
+        <v>66200</v>
       </c>
       <c r="H12" s="3">
-        <v>33600</v>
+        <v>33700</v>
       </c>
       <c r="I12" s="3">
-        <v>19400</v>
+        <v>19300</v>
       </c>
       <c r="J12" s="3">
         <v>12200</v>
@@ -951,26 +951,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>9900</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>641300</v>
+        <v>523600</v>
       </c>
       <c r="E17" s="3">
-        <v>518700</v>
+        <v>481300</v>
       </c>
       <c r="F17" s="3">
-        <v>504300</v>
+        <v>456000</v>
       </c>
       <c r="G17" s="3">
-        <v>236300</v>
+        <v>213800</v>
       </c>
       <c r="H17" s="3">
-        <v>112000</v>
+        <v>100700</v>
       </c>
       <c r="I17" s="3">
-        <v>77300</v>
+        <v>64700</v>
       </c>
       <c r="J17" s="3">
-        <v>38900</v>
+        <v>36300</v>
       </c>
       <c r="K17" s="3">
         <v>25300</v>
@@ -1093,22 +1093,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>642100</v>
+        <v>641000</v>
       </c>
       <c r="E18" s="3">
-        <v>457600</v>
+        <v>457700</v>
       </c>
       <c r="F18" s="3">
-        <v>408100</v>
+        <v>408200</v>
       </c>
       <c r="G18" s="3">
-        <v>188200</v>
+        <v>189300</v>
       </c>
       <c r="H18" s="3">
         <v>24100</v>
       </c>
       <c r="I18" s="3">
-        <v>26800</v>
+        <v>26700</v>
       </c>
       <c r="J18" s="3">
         <v>1100</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4300</v>
+        <v>-2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-27000</v>
+        <v>19300</v>
       </c>
       <c r="F20" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>-2200</v>
+        <v>1500</v>
       </c>
       <c r="H20" s="3">
-        <v>-1300</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="J20" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1195,22 +1195,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>654200</v>
+        <v>651400</v>
       </c>
       <c r="E21" s="3">
-        <v>437700</v>
+        <v>445400</v>
       </c>
       <c r="F21" s="3">
-        <v>413100</v>
+        <v>413200</v>
       </c>
       <c r="G21" s="3">
-        <v>189500</v>
+        <v>191300</v>
       </c>
       <c r="H21" s="3">
-        <v>24900</v>
+        <v>25000</v>
       </c>
       <c r="I21" s="3">
-        <v>26800</v>
+        <v>26700</v>
       </c>
       <c r="J21" s="3">
         <v>1000</v>
@@ -1236,26 +1236,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1279,22 +1279,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>646400</v>
+        <v>643600</v>
       </c>
       <c r="E23" s="3">
-        <v>430700</v>
+        <v>428500</v>
       </c>
       <c r="F23" s="3">
-        <v>408400</v>
+        <v>408500</v>
       </c>
       <c r="G23" s="3">
-        <v>186000</v>
+        <v>187100</v>
       </c>
       <c r="H23" s="3">
         <v>22800</v>
       </c>
       <c r="I23" s="3">
-        <v>25700</v>
+        <v>25600</v>
       </c>
       <c r="J23" s="3">
         <v>400</v>
@@ -1321,7 +1321,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>96000</v>
+        <v>95800</v>
       </c>
       <c r="E24" s="3">
         <v>53100</v>
@@ -1330,7 +1330,7 @@
         <v>48100</v>
       </c>
       <c r="G24" s="3">
-        <v>16000</v>
+        <v>16100</v>
       </c>
       <c r="H24" s="3">
         <v>1600</v>
@@ -1405,22 +1405,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>550400</v>
+        <v>547800</v>
       </c>
       <c r="E26" s="3">
-        <v>377600</v>
+        <v>375400</v>
       </c>
       <c r="F26" s="3">
         <v>360400</v>
       </c>
       <c r="G26" s="3">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="H26" s="3">
-        <v>21200</v>
+        <v>21300</v>
       </c>
       <c r="I26" s="3">
-        <v>17800</v>
+        <v>17700</v>
       </c>
       <c r="J26" s="3">
         <v>-1000</v>
@@ -1447,16 +1447,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>549000</v>
+        <v>548100</v>
       </c>
       <c r="E27" s="3">
-        <v>375300</v>
+        <v>375400</v>
       </c>
       <c r="F27" s="3">
         <v>360400</v>
       </c>
       <c r="G27" s="3">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="H27" s="3">
         <v>18400</v>
@@ -1465,7 +1465,7 @@
         <v>4700</v>
       </c>
       <c r="J27" s="3">
-        <v>-7200</v>
+        <v>-7100</v>
       </c>
       <c r="K27" s="3">
         <v>-14900</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4300</v>
+        <v>2600</v>
       </c>
       <c r="E32" s="3">
-        <v>27000</v>
+        <v>-19300</v>
       </c>
       <c r="F32" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>2200</v>
+        <v>-1500</v>
       </c>
       <c r="H32" s="3">
-        <v>1300</v>
+        <v>-1300</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="J32" s="3">
-        <v>600</v>
+        <v>-600</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>549000</v>
+        <v>548100</v>
       </c>
       <c r="E33" s="3">
-        <v>375300</v>
+        <v>375400</v>
       </c>
       <c r="F33" s="3">
         <v>360400</v>
       </c>
       <c r="G33" s="3">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="H33" s="3">
-        <v>18400</v>
+        <v>21300</v>
       </c>
       <c r="I33" s="3">
-        <v>4700</v>
+        <v>17700</v>
       </c>
       <c r="J33" s="3">
-        <v>-7200</v>
+        <v>-1000</v>
       </c>
       <c r="K33" s="3">
         <v>-14900</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>549000</v>
+        <v>548100</v>
       </c>
       <c r="E35" s="3">
-        <v>375300</v>
+        <v>375400</v>
       </c>
       <c r="F35" s="3">
         <v>360400</v>
       </c>
       <c r="G35" s="3">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="H35" s="3">
-        <v>18400</v>
+        <v>21300</v>
       </c>
       <c r="I35" s="3">
-        <v>4700</v>
+        <v>17700</v>
       </c>
       <c r="J35" s="3">
-        <v>-7200</v>
+        <v>-1000</v>
       </c>
       <c r="K35" s="3">
         <v>-14900</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6322600</v>
+        <v>632100</v>
       </c>
       <c r="E41" s="3">
-        <v>7144300</v>
+        <v>645000</v>
       </c>
       <c r="F41" s="3">
-        <v>7602700</v>
+        <v>584200</v>
       </c>
       <c r="G41" s="3">
-        <v>5580800</v>
+        <v>133400</v>
       </c>
       <c r="H41" s="3">
-        <v>1911100</v>
+        <v>46500</v>
       </c>
       <c r="I41" s="3">
-        <v>1537100</v>
+        <v>27500</v>
       </c>
       <c r="J41" s="3">
-        <v>968400</v>
+        <v>48000</v>
       </c>
       <c r="K41" s="3">
         <v>451800</v>
@@ -1950,22 +1950,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>417200</v>
+        <v>5803100</v>
       </c>
       <c r="E42" s="3">
-        <v>91400</v>
+        <v>6504500</v>
       </c>
       <c r="F42" s="3">
-        <v>163600</v>
+        <v>7032900</v>
       </c>
       <c r="G42" s="3">
-        <v>38500</v>
+        <v>5479900</v>
       </c>
       <c r="H42" s="3">
-        <v>12000</v>
+        <v>1866800</v>
       </c>
       <c r="I42" s="3">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5472400</v>
+        <v>5463000</v>
       </c>
       <c r="E43" s="3">
-        <v>4683400</v>
+        <v>4681800</v>
       </c>
       <c r="F43" s="3">
-        <v>5137100</v>
+        <v>5074200</v>
       </c>
       <c r="G43" s="3">
-        <v>1040400</v>
+        <v>3469800</v>
       </c>
       <c r="H43" s="3">
-        <v>238000</v>
+        <v>762100</v>
       </c>
       <c r="I43" s="3">
-        <v>107300</v>
+        <v>467000</v>
       </c>
       <c r="J43" s="3">
-        <v>51300</v>
+        <v>417100</v>
       </c>
       <c r="K43" s="3">
         <v>104400</v>
@@ -2033,26 +2033,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>24500</v>
+        <v>25100</v>
       </c>
       <c r="E45" s="3">
-        <v>14500</v>
+        <v>17500</v>
       </c>
       <c r="F45" s="3">
-        <v>9700</v>
+        <v>72800</v>
       </c>
       <c r="G45" s="3">
-        <v>1500</v>
+        <v>54000</v>
       </c>
       <c r="H45" s="3">
-        <v>1600</v>
+        <v>15500</v>
       </c>
       <c r="I45" s="3">
-        <v>1100</v>
+        <v>1540500</v>
       </c>
       <c r="J45" s="3">
-        <v>500</v>
+        <v>927600</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12236700</v>
+        <v>11923400</v>
       </c>
       <c r="E46" s="3">
-        <v>11933600</v>
+        <v>11848900</v>
       </c>
       <c r="F46" s="3">
-        <v>12913100</v>
+        <v>12764300</v>
       </c>
       <c r="G46" s="3">
-        <v>6661100</v>
+        <v>9137000</v>
       </c>
       <c r="H46" s="3">
-        <v>2162700</v>
+        <v>2691000</v>
       </c>
       <c r="I46" s="3">
-        <v>1653100</v>
+        <v>2035000</v>
       </c>
       <c r="J46" s="3">
-        <v>1020100</v>
+        <v>1392700</v>
       </c>
       <c r="K46" s="3">
         <v>556800</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>33000</v>
+        <v>322900</v>
       </c>
       <c r="E47" s="3">
-        <v>35500</v>
+        <v>117300</v>
       </c>
       <c r="F47" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2414000</v>
+        <v>153000</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>537900</v>
+        <v>12800</v>
       </c>
       <c r="I47" s="3">
-        <v>395800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>372900</v>
+        <v>7600</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>16900</v>
@@ -2202,19 +2202,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>44800</v>
+        <v>44700</v>
       </c>
       <c r="E48" s="3">
-        <v>43900</v>
+        <v>44000</v>
       </c>
       <c r="F48" s="3">
         <v>53800</v>
       </c>
       <c r="G48" s="3">
-        <v>40700</v>
+        <v>40900</v>
       </c>
       <c r="H48" s="3">
-        <v>35800</v>
+        <v>35900</v>
       </c>
       <c r="I48" s="3">
         <v>2900</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>132000</v>
+        <v>121800</v>
       </c>
       <c r="E52" s="3">
-        <v>98100</v>
+        <v>92000</v>
       </c>
       <c r="F52" s="3">
-        <v>48200</v>
+        <v>43300</v>
       </c>
       <c r="G52" s="3">
-        <v>30600</v>
+        <v>19400</v>
       </c>
       <c r="H52" s="3">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="I52" s="3">
-        <v>7700</v>
+        <v>2700</v>
       </c>
       <c r="J52" s="3">
-        <v>5900</v>
+        <v>1400</v>
       </c>
       <c r="K52" s="3">
         <v>4200</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12455700</v>
+        <v>12434400</v>
       </c>
       <c r="E54" s="3">
-        <v>12118100</v>
+        <v>12119900</v>
       </c>
       <c r="F54" s="3">
-        <v>13020300</v>
+        <v>13021500</v>
       </c>
       <c r="G54" s="3">
-        <v>9147600</v>
+        <v>9200900</v>
       </c>
       <c r="H54" s="3">
-        <v>2744100</v>
+        <v>2747400</v>
       </c>
       <c r="I54" s="3">
-        <v>2059700</v>
+        <v>2051100</v>
       </c>
       <c r="J54" s="3">
-        <v>1400800</v>
+        <v>1398100</v>
       </c>
       <c r="K54" s="3">
         <v>579100</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8262500</v>
+        <v>8269700</v>
       </c>
       <c r="E57" s="3">
-        <v>8857600</v>
+        <v>8899300</v>
       </c>
       <c r="F57" s="3">
-        <v>8606900</v>
+        <v>8719300</v>
       </c>
       <c r="G57" s="3">
-        <v>6529600</v>
+        <v>6579000</v>
       </c>
       <c r="H57" s="3">
-        <v>2170100</v>
+        <v>2174800</v>
       </c>
       <c r="I57" s="3">
-        <v>1695900</v>
+        <v>1688800</v>
       </c>
       <c r="J57" s="3">
-        <v>1071200</v>
+        <v>1069100</v>
       </c>
       <c r="K57" s="3">
         <v>531900</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>724700</v>
+        <v>738100</v>
       </c>
       <c r="E58" s="3">
-        <v>318100</v>
+        <v>332200</v>
       </c>
       <c r="F58" s="3">
-        <v>1388100</v>
+        <v>1400700</v>
       </c>
       <c r="G58" s="3">
-        <v>1402300</v>
+        <v>1419000</v>
       </c>
       <c r="H58" s="3">
-        <v>188400</v>
+        <v>188600</v>
       </c>
       <c r="I58" s="3">
-        <v>202100</v>
+        <v>201300</v>
       </c>
       <c r="J58" s="3">
-        <v>197800</v>
+        <v>197400</v>
       </c>
       <c r="K58" s="3">
         <v>20700</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300400</v>
+        <v>85100</v>
       </c>
       <c r="E59" s="3">
-        <v>252500</v>
+        <v>64400</v>
       </c>
       <c r="F59" s="3">
-        <v>311900</v>
+        <v>91100</v>
       </c>
       <c r="G59" s="3">
-        <v>122000</v>
+        <v>57000</v>
       </c>
       <c r="H59" s="3">
-        <v>36800</v>
+        <v>10800</v>
       </c>
       <c r="I59" s="3">
-        <v>20600</v>
+        <v>7300</v>
       </c>
       <c r="J59" s="3">
-        <v>9900</v>
+        <v>700</v>
       </c>
       <c r="K59" s="3">
         <v>4600</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9287500</v>
+        <v>9271600</v>
       </c>
       <c r="E60" s="3">
-        <v>9428200</v>
+        <v>9429600</v>
       </c>
       <c r="F60" s="3">
-        <v>10306900</v>
+        <v>10307900</v>
       </c>
       <c r="G60" s="3">
-        <v>8053900</v>
+        <v>8107500</v>
       </c>
       <c r="H60" s="3">
-        <v>2395200</v>
+        <v>2390700</v>
       </c>
       <c r="I60" s="3">
-        <v>1918700</v>
+        <v>1909400</v>
       </c>
       <c r="J60" s="3">
-        <v>1278900</v>
+        <v>1275400</v>
       </c>
       <c r="K60" s="3">
         <v>557200</v>
@@ -2700,19 +2700,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>20100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>22100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17400</v>
+        <v>700</v>
       </c>
       <c r="E62" s="3">
-        <v>14800</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
-        <v>22400</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>28500</v>
+        <v>900</v>
       </c>
       <c r="H62" s="3">
-        <v>22100</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>7100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>500</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9305300</v>
+        <v>9289000</v>
       </c>
       <c r="E66" s="3">
-        <v>9443000</v>
+        <v>9444400</v>
       </c>
       <c r="F66" s="3">
-        <v>10329300</v>
+        <v>10330300</v>
       </c>
       <c r="G66" s="3">
-        <v>8082300</v>
+        <v>8129400</v>
       </c>
       <c r="H66" s="3">
-        <v>2417300</v>
+        <v>2420200</v>
       </c>
       <c r="I66" s="3">
-        <v>1918700</v>
+        <v>1910600</v>
       </c>
       <c r="J66" s="3">
-        <v>1278900</v>
+        <v>1276400</v>
       </c>
       <c r="K66" s="3">
         <v>561300</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>160300</v>
+        <v>159700</v>
       </c>
       <c r="J70" s="3">
-        <v>151800</v>
+        <v>151500</v>
       </c>
       <c r="K70" s="3">
         <v>42200</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1456800</v>
+        <v>1454300</v>
       </c>
       <c r="E72" s="3">
-        <v>907800</v>
+        <v>907900</v>
       </c>
       <c r="F72" s="3">
         <v>532500</v>
       </c>
       <c r="G72" s="3">
-        <v>172100</v>
+        <v>173100</v>
       </c>
       <c r="H72" s="3">
         <v>2100</v>
       </c>
       <c r="I72" s="3">
-        <v>-19100</v>
+        <v>-19000</v>
       </c>
       <c r="J72" s="3">
-        <v>-29600</v>
+        <v>-29500</v>
       </c>
       <c r="K72" s="3">
         <v>-24000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3150400</v>
+        <v>3145100</v>
       </c>
       <c r="E76" s="3">
-        <v>2675100</v>
+        <v>2675500</v>
       </c>
       <c r="F76" s="3">
-        <v>2691000</v>
+        <v>2691200</v>
       </c>
       <c r="G76" s="3">
-        <v>1065300</v>
+        <v>1071500</v>
       </c>
       <c r="H76" s="3">
-        <v>326800</v>
+        <v>327200</v>
       </c>
       <c r="I76" s="3">
         <v>-19200</v>
       </c>
       <c r="J76" s="3">
-        <v>-29900</v>
+        <v>-29800</v>
       </c>
       <c r="K76" s="3">
         <v>-24400</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>549000</v>
+        <v>548100</v>
       </c>
       <c r="E81" s="3">
-        <v>375300</v>
+        <v>375400</v>
       </c>
       <c r="F81" s="3">
         <v>360400</v>
       </c>
       <c r="G81" s="3">
-        <v>170000</v>
+        <v>171000</v>
       </c>
       <c r="H81" s="3">
-        <v>18400</v>
+        <v>21300</v>
       </c>
       <c r="I81" s="3">
-        <v>4700</v>
+        <v>17700</v>
       </c>
       <c r="J81" s="3">
-        <v>-7200</v>
+        <v>-1000</v>
       </c>
       <c r="K81" s="3">
         <v>-14900</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7800</v>
+        <v>19700</v>
       </c>
       <c r="E83" s="3">
-        <v>7000</v>
+        <v>18300</v>
       </c>
       <c r="F83" s="3">
-        <v>4700</v>
+        <v>15100</v>
       </c>
       <c r="G83" s="3">
-        <v>3500</v>
+        <v>10100</v>
       </c>
       <c r="H83" s="3">
-        <v>2100</v>
+        <v>8400</v>
       </c>
       <c r="I83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-812600</v>
+        <v>-811300</v>
       </c>
       <c r="E89" s="3">
-        <v>445600</v>
+        <v>445700</v>
       </c>
       <c r="F89" s="3">
-        <v>770900</v>
+        <v>771000</v>
       </c>
       <c r="G89" s="3">
-        <v>2623200</v>
+        <v>2638400</v>
       </c>
       <c r="H89" s="3">
-        <v>252500</v>
+        <v>252800</v>
       </c>
       <c r="I89" s="3">
-        <v>573200</v>
+        <v>570800</v>
       </c>
       <c r="J89" s="3">
-        <v>237900</v>
+        <v>237500</v>
       </c>
       <c r="K89" s="3">
         <v>179200</v>
@@ -3818,7 +3818,7 @@
         <v>-9000</v>
       </c>
       <c r="G91" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="H91" s="3">
         <v>-15200</v>
@@ -3827,7 +3827,7 @@
         <v>-2400</v>
       </c>
       <c r="J91" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="K91" s="3">
         <v>-500</v>
@@ -3935,7 +3935,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-313400</v>
+        <v>-312900</v>
       </c>
       <c r="E94" s="3">
         <v>12000</v>
@@ -3944,7 +3944,7 @@
         <v>-123600</v>
       </c>
       <c r="G94" s="3">
-        <v>-31300</v>
+        <v>-31500</v>
       </c>
       <c r="H94" s="3">
         <v>-20500</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>295900</v>
+        <v>295400</v>
       </c>
       <c r="E100" s="3">
-        <v>-898800</v>
+        <v>-899000</v>
       </c>
       <c r="F100" s="3">
-        <v>1353400</v>
+        <v>1353500</v>
       </c>
       <c r="G100" s="3">
-        <v>1078000</v>
+        <v>1084300</v>
       </c>
       <c r="H100" s="3">
-        <v>147700</v>
+        <v>147900</v>
       </c>
       <c r="I100" s="3">
         <v>4600</v>
       </c>
       <c r="J100" s="3">
-        <v>276400</v>
+        <v>275900</v>
       </c>
       <c r="K100" s="3">
         <v>18900</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-821600</v>
+        <v>-820200</v>
       </c>
       <c r="E102" s="3">
-        <v>-458500</v>
+        <v>-458600</v>
       </c>
       <c r="F102" s="3">
-        <v>2022200</v>
+        <v>2022400</v>
       </c>
       <c r="G102" s="3">
-        <v>3669700</v>
+        <v>3691100</v>
       </c>
       <c r="H102" s="3">
-        <v>374000</v>
+        <v>374400</v>
       </c>
       <c r="I102" s="3">
-        <v>568700</v>
+        <v>566300</v>
       </c>
       <c r="J102" s="3">
-        <v>516500</v>
+        <v>515500</v>
       </c>
       <c r="K102" s="3">
         <v>197300</v>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -656,58 +656,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +717,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1541400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1164600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>939000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>864200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>403100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>124800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>37300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E9" s="3">
         <v>80100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>90200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>106300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>65900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1434800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1084500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>848700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>757800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>337300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +874,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E12" s="3">
         <v>184400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>156700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>103300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>66200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7900</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,35 +961,38 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>9900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -997,26 +1019,26 @@
         <v>7800</v>
       </c>
       <c r="E15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F15" s="3">
         <v>7000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>688900</v>
+      </c>
+      <c r="E17" s="3">
         <v>523600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>481300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>456000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>213800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>64700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>852500</v>
+      </c>
+      <c r="E18" s="3">
         <v>641000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>457700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>408200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>189300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1179,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>19300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,39 +1221,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>835800</v>
+      </c>
+      <c r="E21" s="3">
         <v>651400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>445400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>413200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>191300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1266,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,8 +1296,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>828000</v>
+      </c>
+      <c r="E23" s="3">
         <v>643600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>428500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>408500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>187100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E24" s="3">
         <v>95800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>699500</v>
+      </c>
+      <c r="E26" s="3">
         <v>547800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>375400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>360400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>171000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E27" s="3">
         <v>548100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>375400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>360400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>171000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1716,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-19300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E33" s="3">
         <v>548100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>375400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>360400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>171000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E35" s="3">
         <v>548100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>375400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>360400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>171000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1896,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,38 +1987,39 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1504800</v>
+      </c>
+      <c r="E41" s="3">
         <v>632100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>645000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>584200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>451800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,41 +2029,44 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8877500</v>
+      </c>
+      <c r="E42" s="3">
         <v>5803100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6504500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7032900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5479900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1866800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1985,39 +2074,42 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9460400</v>
+      </c>
+      <c r="E43" s="3">
         <v>5463000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4681800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5074200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3469800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>762100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>467000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>417100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>104400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2149,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E45" s="3">
         <v>25100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>54000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1540500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>927600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,41 +2209,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19880200</v>
+      </c>
+      <c r="E46" s="3">
         <v>11923400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11848900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12764300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9137000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2691000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2035000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1392700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>556800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>384200</v>
+      </c>
+      <c r="E47" s="3">
         <v>322900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>117300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>153000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>12800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>16900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E48" s="3">
         <v>44700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,29 +2344,32 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>9200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>200</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -2267,8 +2377,8 @@
       <c r="K49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E52" s="3">
         <v>121800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>92000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,39 +2569,42 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20560200</v>
+      </c>
+      <c r="E54" s="3">
         <v>12434400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12119900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13021500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9200900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2747400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2051100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1398100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>579100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,38 +2655,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15130400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8269700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8899300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8719300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6579000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2174800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1688800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1069100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>531900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,39 +2697,42 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1084200</v>
+      </c>
+      <c r="E58" s="3">
         <v>738100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>332200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1400700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1419000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>188600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>201300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>197400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,39 +2742,42 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E59" s="3">
         <v>85100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>64400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,41 +2787,44 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16936800</v>
+      </c>
+      <c r="E60" s="3">
         <v>9271600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9429600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10307900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8107500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2390700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1909400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1275400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>557200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -2693,39 +2832,42 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E61" s="3">
         <v>15800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>4100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2735,41 +2877,44 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16954900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9289000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9444400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10330300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8129400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2420200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1910600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1276400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>561300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3069,17 +3236,17 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>159700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>151500</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>42200</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,39 +3301,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1886400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1454300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>907900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>532500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>173100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-19000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-24000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,39 +3481,42 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3606200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3145100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2675500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2691200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1071500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>327200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-19200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-29800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-24400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3571,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3621,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E81" s="3">
         <v>548100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>375400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>360400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>171000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,37 +3688,38 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>19700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>500</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3955,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-811300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>445700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>771000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2638400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>252800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>570800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>237500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>179200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4022,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4154,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-312900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-123600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4398,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>295400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-899000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1353500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1084300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>147900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>275900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,38 +4443,41 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>8500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>21400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2800</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -4240,39 +4488,42 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-820200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-458600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2022400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3691100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>374400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>566300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>515500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>197300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -1016,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>7800</v>
+        <v>9000</v>
       </c>
       <c r="E15" s="3">
         <v>7800</v>
@@ -1231,7 +1231,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>835800</v>
+        <v>837000</v>
       </c>
       <c r="E21" s="3">
         <v>651400</v>
@@ -2039,7 +2039,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8877500</v>
+        <v>8972700</v>
       </c>
       <c r="E42" s="3">
         <v>5803100</v>
@@ -2084,7 +2084,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9460400</v>
+        <v>9338800</v>
       </c>
       <c r="E43" s="3">
         <v>5463000</v>
@@ -2219,7 +2219,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19880200</v>
+        <v>19853700</v>
       </c>
       <c r="E46" s="3">
         <v>11923400</v>
@@ -2264,7 +2264,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>384200</v>
+        <v>289000</v>
       </c>
       <c r="E47" s="3">
         <v>322900</v>
@@ -2309,7 +2309,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>32600</v>
+        <v>56700</v>
       </c>
       <c r="E48" s="3">
         <v>44700</v>
@@ -2354,7 +2354,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E49" s="3">
         <v>9200</v>
@@ -2489,7 +2489,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>263200</v>
+        <v>213700</v>
       </c>
       <c r="E52" s="3">
         <v>121800</v>
@@ -2579,7 +2579,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20560200</v>
+        <v>20438600</v>
       </c>
       <c r="E54" s="3">
         <v>12434400</v>
@@ -2662,7 +2662,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15130400</v>
+        <v>15042100</v>
       </c>
       <c r="E57" s="3">
         <v>8269700</v>
@@ -2752,10 +2752,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>75500</v>
+        <v>461100</v>
       </c>
       <c r="E59" s="3">
-        <v>85100</v>
+        <v>87200</v>
       </c>
       <c r="F59" s="3">
         <v>64400</v>
@@ -2797,7 +2797,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16936800</v>
+        <v>16815100</v>
       </c>
       <c r="E60" s="3">
         <v>9271600</v>
@@ -2887,7 +2887,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
         <v>700</v>
@@ -3067,7 +3067,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16954900</v>
+        <v>16833300</v>
       </c>
       <c r="E66" s="3">
         <v>9289000</v>
@@ -3694,8 +3694,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>19900</v>
       </c>
       <c r="E83" s="3">
         <v>19700</v>
@@ -3964,8 +3964,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>3990500</v>
       </c>
       <c r="E89" s="3">
         <v>-811300</v>
@@ -4028,8 +4028,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-21600</v>
       </c>
       <c r="E91" s="3">
         <v>-10000</v>
@@ -4163,8 +4163,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>13400</v>
       </c>
       <c r="E94" s="3">
         <v>-312900</v>
@@ -4407,8 +4407,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>9100</v>
       </c>
       <c r="E100" s="3">
         <v>295400</v>
@@ -4452,8 +4452,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-19300</v>
       </c>
       <c r="E101" s="3">
         <v>8500</v>
@@ -4498,7 +4498,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>3993700</v>
       </c>
       <c r="E102" s="3">
         <v>-820200</v>

--- a/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUTU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>FUTU</t>
   </si>
@@ -656,61 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,42 +720,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2709500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1541400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1164600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>939000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>864200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>403100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>124800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E9" s="3">
         <v>106600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>80100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>90200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>106300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>65900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2557300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1434800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1084500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>848700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>757800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>337300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,41 +887,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>245200</v>
+      </c>
+      <c r="E12" s="3">
         <v>192300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>184400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>156700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>103300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>66200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,9 +980,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -976,26 +995,26 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>9900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1009,39 +1028,42 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E15" s="3">
         <v>9000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900400</v>
+      </c>
+      <c r="E17" s="3">
         <v>688900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>523600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>481300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>456000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>213800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>64700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1809000</v>
+      </c>
+      <c r="E18" s="3">
         <v>852500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>641000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>457700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>408200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>189300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,41 +1212,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E20" s="3">
         <v>24500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>19300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,42 +1257,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1764500</v>
+      </c>
+      <c r="E21" s="3">
         <v>837000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>651400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>445400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>413200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>191300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,9 +1305,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1299,8 +1338,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1755200</v>
+      </c>
+      <c r="E23" s="3">
         <v>828000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>643600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>428500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>408500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>187100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E24" s="3">
         <v>128500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>95800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>53100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1700</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1452000</v>
+      </c>
+      <c r="E26" s="3">
         <v>699500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>547800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>375400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>360400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>171000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1456700</v>
+      </c>
+      <c r="E27" s="3">
         <v>700800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>548100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>375400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>360400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>171000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,42 +1785,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-24500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-19300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1456600</v>
+      </c>
+      <c r="E33" s="3">
         <v>700800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>548100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>375400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>360400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>171000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1456600</v>
+      </c>
+      <c r="E35" s="3">
         <v>700800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>548100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>375400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>360400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>171000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,47 +1977,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,41 +2073,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1344600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1504800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>632100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>645000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>584200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>451800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,44 +2118,47 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14831700</v>
+      </c>
+      <c r="E42" s="3">
         <v>8972700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5803100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6504500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7032900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5479900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1866800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2077,42 +2166,45 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11855600</v>
+      </c>
+      <c r="E43" s="3">
         <v>9338800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5463000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4681800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5074200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3469800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>762100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>467000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>417100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>104400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2152,8 +2247,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E45" s="3">
         <v>37300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>17500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>54000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1540500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>927600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,44 +2310,47 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28072100</v>
+      </c>
+      <c r="E46" s="3">
         <v>19853700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11923400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11848900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12764300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9137000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2691000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2035000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1392700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>556800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3">
-        <v>0</v>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>741100</v>
+      </c>
+      <c r="E47" s="3">
         <v>289000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>322900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>117300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>153000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>12800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>16900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E48" s="3">
         <v>56700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,32 +2454,35 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E49" s="3">
         <v>11000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>200</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -2380,8 +2490,8 @@
       <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>200</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>386900</v>
+      </c>
+      <c r="E52" s="3">
         <v>213700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>121800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>92000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>43300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,42 +2694,45 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29349100</v>
+      </c>
+      <c r="E54" s="3">
         <v>20438600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12434400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12119900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13021500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9200900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2747400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2051100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1398100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>579100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,41 +2785,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21177500</v>
+      </c>
+      <c r="E57" s="3">
         <v>15042100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8269700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8899300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8719300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6579000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2174800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1688800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1069100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>531900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,42 +2830,45 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2195200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1084200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>738100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>332200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1419000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>188600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>201300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>197400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,42 +2878,45 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>419400</v>
+      </c>
+      <c r="E59" s="3">
         <v>461100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>87200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>64400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>91100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,44 +2926,47 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24115300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16815100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9271600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9429600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10307900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8107500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2390700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1909400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1275400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>557200</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3">
-        <v>0</v>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O60" s="3">
         <v>0</v>
@@ -2835,42 +2974,45 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E61" s="3">
         <v>17100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>4100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2880,44 +3022,47 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24168700</v>
+      </c>
+      <c r="E66" s="3">
         <v>16833300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9289000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9444400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10330300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8129400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2420200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1910600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1276400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>561300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3239,17 +3406,17 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>159700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>151500</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>42200</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,42 +3474,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3339200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1886400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1454300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>907900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>532500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>173100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-19000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,42 +3666,45 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5139300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3606200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3145100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2675500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2691200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1071500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>327200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-19200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-29800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-24400</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,47 +3762,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,42 +3815,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1456600</v>
+      </c>
+      <c r="E81" s="3">
         <v>700800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>548100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>375400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>360400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>171000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,40 +3886,41 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>19900</v>
+        <v>28600</v>
       </c>
       <c r="E83" s="3">
-        <v>19700</v>
+        <v>22600</v>
       </c>
       <c r="F83" s="3">
+        <v>21900</v>
+      </c>
+      <c r="G83" s="3">
         <v>18300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>500</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,42 +4171,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E89" s="3">
         <v>3990500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-811300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>445700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>771000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2638400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>252800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>570800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>237500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>179200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,41 +4242,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,42 +4383,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-229100</v>
+      </c>
+      <c r="E94" s="3">
         <v>13400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-312900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-123600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,13 +4454,14 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>276400</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,42 +4643,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>295400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-899000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1353500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1084300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>147900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>275900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,41 +4691,44 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-19300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>21400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4491,42 +4739,45 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5593600</v>
+      </c>
+      <c r="E102" s="3">
         <v>3993700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-820200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-458600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2022400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3691100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>374400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>566300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>515500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>197300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
